--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N105_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N105_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.00480724789169</v>
+        <v>4.225781177782399</v>
       </c>
       <c r="D2" t="n">
-        <v>46.4523654840085</v>
+        <v>7.548509391151382</v>
       </c>
       <c r="E2" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F2" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.15097169808491</v>
+        <v>2.299532900938797</v>
       </c>
       <c r="D3" t="n">
-        <v>51.82941057498881</v>
+        <v>8.422279218435682</v>
       </c>
       <c r="E3" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F3" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.75394704043941</v>
+        <v>3.860016394071404</v>
       </c>
       <c r="D4" t="n">
-        <v>58.10176112751199</v>
+        <v>9.441536183220698</v>
       </c>
       <c r="E4" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F4" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>3.834336793697569</v>
+        <v>0.623079728975855</v>
       </c>
       <c r="D5" t="n">
-        <v>3.321365899270786</v>
+        <v>0.5397219586315029</v>
       </c>
       <c r="E5" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F5" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.31380852216589</v>
+        <v>3.138493884851957</v>
       </c>
       <c r="D6" t="n">
-        <v>29.92751212079897</v>
+        <v>4.863220719629833</v>
       </c>
       <c r="E6" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F6" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8.902246907382429</v>
+        <v>1.446615122449645</v>
       </c>
       <c r="D7" t="n">
-        <v>50.25254961577077</v>
+        <v>8.16603931256275</v>
       </c>
       <c r="E7" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F7" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4.475884805316729</v>
+        <v>0.7273312808639686</v>
       </c>
       <c r="D8" t="n">
-        <v>39.04973218866106</v>
+        <v>6.345581480657422</v>
       </c>
       <c r="E8" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F8" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>14.00526990446093</v>
+        <v>2.275856359474902</v>
       </c>
       <c r="D9" t="n">
-        <v>13.56955420048783</v>
+        <v>2.205052557579272</v>
       </c>
       <c r="E9" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F9" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.84082207965583</v>
+        <v>2.411633587944072</v>
       </c>
       <c r="D10" t="n">
-        <v>37.42848715611736</v>
+        <v>6.08212916286907</v>
       </c>
       <c r="E10" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F10" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>23.71683721847818</v>
+        <v>3.853986048002704</v>
       </c>
       <c r="D11" t="n">
-        <v>14.14063988856498</v>
+        <v>2.29785398189181</v>
       </c>
       <c r="E11" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F11" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>16.62077013859466</v>
+        <v>2.700875147521633</v>
       </c>
       <c r="D12" t="n">
-        <v>31.96004450003856</v>
+        <v>5.193507231256265</v>
       </c>
       <c r="E12" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F12" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>26.8623696838728</v>
+        <v>4.36513507362933</v>
       </c>
       <c r="D13" t="n">
-        <v>18.46328699215902</v>
+        <v>3.000284136225841</v>
       </c>
       <c r="E13" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F13" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>28.32401807653709</v>
+        <v>4.602652937437278</v>
       </c>
       <c r="D14" t="n">
-        <v>21.38600269127242</v>
+        <v>3.475225437331769</v>
       </c>
       <c r="E14" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F14" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>11.33839563323201</v>
+        <v>1.842489290400201</v>
       </c>
       <c r="D15" t="n">
-        <v>11.90994929159635</v>
+        <v>1.935366759884408</v>
       </c>
       <c r="E15" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F15" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>21.70714147250908</v>
+        <v>3.527410489282726</v>
       </c>
       <c r="D16" t="n">
-        <v>22.33123603877114</v>
+        <v>3.628825856300311</v>
       </c>
       <c r="E16" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F16" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>29.84508105949499</v>
+        <v>4.849825672167936</v>
       </c>
       <c r="D17" t="n">
-        <v>29.65732655002498</v>
+        <v>4.81931556437906</v>
       </c>
       <c r="E17" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F17" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>2.912830787402727</v>
+        <v>0.4733350029529432</v>
       </c>
       <c r="D18" t="n">
-        <v>3.183875084598792</v>
+        <v>0.5173797012473038</v>
       </c>
       <c r="E18" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F18" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>1.927654014065502</v>
+        <v>0.313243777285644</v>
       </c>
       <c r="D19" t="n">
-        <v>1.724417893374565</v>
+        <v>0.2802179076733669</v>
       </c>
       <c r="E19" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F19" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>12.29705648037879</v>
+        <v>1.998271678061553</v>
       </c>
       <c r="D20" t="n">
-        <v>11.58853386599679</v>
+        <v>1.883136753224478</v>
       </c>
       <c r="E20" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F20" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>22.84312357759482</v>
+        <v>3.712007581359158</v>
       </c>
       <c r="D21" t="n">
-        <v>25.30644982784777</v>
+        <v>4.112298097025262</v>
       </c>
       <c r="E21" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F21" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>33.70712494363974</v>
+        <v>5.477407803341458</v>
       </c>
       <c r="D22" t="n">
-        <v>33.21860937439349</v>
+        <v>5.398024023338942</v>
       </c>
       <c r="E22" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F22" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>37.49815552597939</v>
+        <v>6.093450272971651</v>
       </c>
       <c r="D23" t="n">
-        <v>36.74979191643438</v>
+        <v>5.971841186420588</v>
       </c>
       <c r="E23" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F23" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>25.02735763045773</v>
+        <v>4.066945614949381</v>
       </c>
       <c r="D24" t="n">
-        <v>26.69201463994718</v>
+        <v>4.337452378991417</v>
       </c>
       <c r="E24" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F24" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>45.26372950245114</v>
+        <v>7.35535604414831</v>
       </c>
       <c r="D25" t="n">
-        <v>44.50971120042833</v>
+        <v>7.232828070069605</v>
       </c>
       <c r="E25" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F25" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>46.98255575734917</v>
+        <v>7.63466531056924</v>
       </c>
       <c r="D26" t="n">
-        <v>46.33204506296362</v>
+        <v>7.528957322731589</v>
       </c>
       <c r="E26" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F26" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>51.57969326575406</v>
+        <v>8.381700155685035</v>
       </c>
       <c r="D27" t="n">
-        <v>50.85583497950053</v>
+        <v>8.264073184168836</v>
       </c>
       <c r="E27" t="n">
-        <v>13.25873350609556</v>
+        <v>2.154544194740529</v>
       </c>
       <c r="F27" t="n">
-        <v>16.12207551106458</v>
+        <v>2.619837270547994</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
